--- a/Taetigkeitsuebersicht_Angelo.xlsx
+++ b/Taetigkeitsuebersicht_Angelo.xlsx
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +202,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -675,39 +685,775 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6" t="inlineStr">
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Kick-off-Meeting: Projektidee besprochen, technische Anforderungen aufgenommen, Technologie-Stack festgelegt (PHP, MySQL, XAMPP)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>17.02.2026</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Anforderungsanalyse: Kernfeatures besprochen, Datenbankstruktur skizziert, Seitenstruktur geplant</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>ERM-Diagramm erstellt (Chen-Notation): Entities Kunde, Artikel, Bestellung mit Attributen und Kardinalitäten modelliert</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>03.03.2026</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>SQL-Skript (database.sql) erstellt: Datenbank beseshop, Tabellen customers, products, orders mit PK, FK und UNIQUE-Constraints</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>03.03.2026</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Review des Datenbankschemas mit Vincent, Feedback eingearbeitet</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Beispieldaten eingefügt: 5 Produkte (B001-B005) und 2 Testkunden, Passwort-Hashing mit password_hash()</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>17.03.2026</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>config.php erstellt (PDO-Datenbankverbindung, Session-Start), header.php und footer.php als Template-System aufgebaut</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>17.03.2026</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>index.php (Landingpage) implementiert: Hero-Bereich, Feature-Karten (Nachhaltig, Handgemacht, Schnelle Lieferung)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>24.03.2026</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>register.php implementiert: Formular mit Pflichtfeldern, automatische Kundennummern-Generierung (K12345), Duplikatprüfung E-Mail</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>24.03.2026</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>Meilenstein-Review mit Vincent und Julia: Registrierung und Login abgenommen</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>login.php und logout.php implementiert: Session-basierte Authentifizierung mit password_verify(), Weiterleitung nach Login</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>products.php implementiert: Dynamischer Produktkatalog aus DB, Verfügbarkeitsanzeige, In-den-Warenkorb-Button</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Meilenstein-Review: Produktkatalog und Warenkorb mit Vincent und Julia geprüft</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>cart.php implementiert: Session-basierter Warenkorb, Menge ändern, Artikel entfernen, Warenkorb leeren, Badge in Navigation</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>order.php implementiert: Checkout mit Warenkorb- und Einzelprodukt-Modus, Zahlungsmethoden als klickbare Karten, serverseitige Lagerbestandsprüfung</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript für Live-Zusammenfassung im Checkout, Datenbank-Transaktionen für Bestellungen eingebaut</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>order_confirmation.php implementiert: Bestätigungsseite mit Zwei-Spalten-Layout, Unterstützung für Mehrfachbestellungen</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>my_orders.php implementiert: Bestellübersicht mit Stornierungsfunktion, Lagerbestandswiederherstellung bei Stornierung</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>style.css finalisiert: CSS-Variablen, Flexbox, Grid, Media Queries, Checkout-Karten, Alert-Boxen, Responsive Design</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>Bugfix: Try-Catch-Block in config.php für Fehlerbehandlung bei DB-Ausfall (gemeldet von Julia, TF-001)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>Bugfix: number_format() für Preisanzeige und min=1 Validierung für Bestellmengen (TF-002)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Optisches Feedback: Erfolgs- und Fehlermeldungen in order.php hervorgehoben</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Finale Code-Bereinigung und Vorbereitung für Projektabgabe</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>Gesamt:</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>32:00:00</t>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>32:00</t>
         </is>
       </c>
     </row>
@@ -849,7 +1595,7 @@
           <t>Hat die Projektstruktur mitdefiniert und auf Konsistenz geachtet.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="12" t="n"/>
       <c r="F9" s="15" t="n">
         <v>3</v>
       </c>
@@ -890,7 +1636,7 @@
           <t>Review-Feedback hat zu besserer Kommentierung geführt.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="12" t="n"/>
       <c r="F11" s="15" t="n">
         <v>3</v>
       </c>
@@ -931,7 +1677,7 @@
           <t>Datenbankschema im Review geprüft und Verbesserungen vorgeschlagen.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="12" t="n"/>
       <c r="F13" s="15" t="n">
         <v>4</v>
       </c>
@@ -972,7 +1718,7 @@
           <t>Alle Meilensteine kontrolliert und Qualität sichergestellt.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="12" t="n"/>
       <c r="F15" s="15" t="n">
         <v>4</v>
       </c>
@@ -1081,7 +1827,7 @@
           <t>Deckblatt-Vorlage vorgegeben, ansprechend.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="12" t="n"/>
       <c r="F22" s="15" t="n">
         <v>4</v>
       </c>
@@ -1123,7 +1869,7 @@
           <t>Gliederung vorgegeben und kontrolliert.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="15" t="n">
         <v>3</v>
       </c>
@@ -1164,7 +1910,7 @@
           <t>Projektbeschreibung vollständig, gute Struktur.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="12" t="n"/>
       <c r="F26" s="15" t="n">
         <v>4</v>
       </c>
@@ -1206,7 +1952,7 @@
           <t>Implementierungsbeschreibung geprüft und Feedback gegeben.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="12" t="n"/>
       <c r="F28" s="15" t="n">
         <v>3</v>
       </c>
@@ -1248,7 +1994,7 @@
           <t>Fazit und Ausblick sinnvoll formuliert.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="15" t="n">
         <v>4</v>
       </c>
@@ -1358,7 +2104,7 @@
           <t>Koordiniert das Team vorbildlich, regelmäßige Meetings organisiert.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="15" t="n">
         <v>4</v>
       </c>
@@ -1399,7 +2145,7 @@
           <t>Gutes Gesamtverständnis, kann Zusammenhänge gut erklären.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="12" t="n"/>
       <c r="F39" s="15" t="n">
         <v>4</v>
       </c>
@@ -1508,7 +2254,7 @@
           <t>Alle Meetings und Reviews dokumentiert.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="15" t="n">
         <v>3</v>
       </c>
@@ -1550,7 +2296,7 @@
           <t>Tätigkeiten nachvollziehbar beschrieben, Abstimmung mit Team erkennbar.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="12" t="n"/>
       <c r="F48" s="15" t="n">
         <v>4</v>
       </c>
@@ -1678,10 +2424,10 @@
           <t>4. Tätigkeitsbericht (IN)</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="29" t="n"/>
       <c r="F57" s="15" t="n">
         <v>1.4</v>
       </c>
@@ -1713,8 +2459,8 @@
   <mergeCells count="18">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D11:E11"/>
@@ -1867,7 +2613,7 @@
           <t>Hat durch Testing zur Verbesserung der Codestruktur beigetragen.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="12" t="n"/>
       <c r="F9" s="15" t="n">
         <v>3</v>
       </c>
@@ -1908,7 +2654,7 @@
           <t>Fehlermeldungen und Testschritte präzise beschrieben.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="12" t="n"/>
       <c r="F11" s="15" t="n">
         <v>3</v>
       </c>
@@ -1949,7 +2695,7 @@
           <t>Datenbankvalidierung durch Tests abgesichert.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="12" t="n"/>
       <c r="F13" s="15" t="n">
         <v>4</v>
       </c>
@@ -1990,7 +2736,7 @@
           <t>Durch systematisches Testen alle kritischen Fehler gefunden und Behebung bestätigt.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="12" t="n"/>
       <c r="F15" s="15" t="n">
         <v>4</v>
       </c>
@@ -2099,7 +2845,7 @@
           <t>Gestaltung sauber und übersichtlich.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="12" t="n"/>
       <c r="F22" s="15" t="n">
         <v>4</v>
       </c>
@@ -2141,7 +2887,7 @@
           <t>Verzeichnis vollständig.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="15" t="n">
         <v>3</v>
       </c>
@@ -2182,7 +2928,7 @@
           <t>Testprotokoll als Teil der Doku sehr ausführlich.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="12" t="n"/>
       <c r="F26" s="15" t="n">
         <v>4</v>
       </c>
@@ -2224,7 +2970,7 @@
           <t>Testfälle mit Screenshots und Schritten gut dokumentiert.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="12" t="n"/>
       <c r="F28" s="15" t="n">
         <v>3</v>
       </c>
@@ -2266,7 +3012,7 @@
           <t>Testprotokoll vollständig, Kommunikationslogbuch gepflegt.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="15" t="n">
         <v>4</v>
       </c>
@@ -2376,7 +3122,7 @@
           <t>Aktiv in der Kommunikation mit Entwicklung, zeitnahes Feedback.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="15" t="n">
         <v>4</v>
       </c>
@@ -2417,7 +3163,7 @@
           <t>Gutes Verständnis der getesteten Funktionen und Fehlermechanismen.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="12" t="n"/>
       <c r="F39" s="15" t="n">
         <v>3</v>
       </c>
@@ -2526,7 +3272,7 @@
           <t>Alle Testtage lückenlos dokumentiert.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="15" t="n">
         <v>4</v>
       </c>
@@ -2568,7 +3314,7 @@
           <t>Testfälle und Ergebnisse detailliert beschrieben.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="12" t="n"/>
       <c r="F48" s="15" t="n">
         <v>3</v>
       </c>
@@ -2696,10 +3442,10 @@
           <t>4. Tätigkeitsbericht (IN)</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="29" t="n"/>
       <c r="F57" s="15" t="n">
         <v>1.9</v>
       </c>
@@ -2731,8 +3477,8 @@
   <mergeCells count="18">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D11:E11"/>
